--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487641_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487641_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7801</v>
+        <v>5.4686</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9658</v>
+        <v>3.6269</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8144</v>
+        <v>1.8416</v>
       </c>
       <c r="G2" t="n">
         <v>2.5735</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9397</v>
+        <v>-0.2512</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7268</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2129</v>
+        <v>-0.1856</v>
       </c>
       <c r="V2" t="n">
         <v>1.788</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5852</v>
+        <v>4.7279</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7589</v>
+        <v>3.6802</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1736</v>
+        <v>1.0477</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2925</v>
+        <v>5.9118</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3579</v>
+        <v>0.6047</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.0654</v>
+        <v>5.307</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0781</v>
+        <v>6.5316</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9989</v>
+        <v>0.8074</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.9208</v>
+        <v>5.7241</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7856</v>
+        <v>-0.6198</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.641</v>
+        <v>-0.2027</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1446</v>
+        <v>-0.4171</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3582</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.1045</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9345</v>
+        <v>0.2908</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4569</v>
+        <v>0.2532</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4776</v>
+        <v>0.0376</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2239</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4758</v>
+        <v>3.5091</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0077</v>
+        <v>3.0683</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4681</v>
+        <v>0.4408</v>
       </c>
       <c r="G4" t="n">
         <v>2.7358</v>
@@ -766,13 +766,13 @@
         <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9161</v>
+        <v>0.9494</v>
       </c>
       <c r="T4" t="n">
-        <v>0.729</v>
+        <v>0.7896</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1871</v>
+        <v>0.1598</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5642</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2664</v>
+        <v>2.6453</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5186</v>
+        <v>3.1187</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7479</v>
+        <v>-0.4734</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9118</v>
+        <v>0.2925</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6047</v>
+        <v>2.3579</v>
       </c>
       <c r="I5" t="n">
-        <v>5.307</v>
+        <v>-2.0654</v>
       </c>
       <c r="J5" t="n">
-        <v>6.5316</v>
+        <v>1.0781</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8074</v>
+        <v>2.9989</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7241</v>
+        <v>-1.9208</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6198</v>
+        <v>-0.7856</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2027</v>
+        <v>-0.641</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4171</v>
+        <v>-0.1446</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1344</v>
+        <v>1.3582</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1045</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1707</v>
+        <v>0.9946</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9085</v>
+        <v>0.8168</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2622</v>
+        <v>0.1778</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6597</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2324</v>
+        <v>2.5838</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4308</v>
+        <v>2.1911</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8016</v>
+        <v>0.3927</v>
       </c>
       <c r="G6" t="n">
         <v>2.296</v>
@@ -922,13 +922,13 @@
         <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0065</v>
+        <v>1.3579</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0935</v>
+        <v>0.8538</v>
       </c>
       <c r="U6" t="n">
-        <v>0.913</v>
+        <v>0.5042</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4582</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5591</v>
+        <v>1.0191</v>
       </c>
       <c r="E7" t="n">
-        <v>1.58</v>
+        <v>1.0399</v>
       </c>
       <c r="F7" t="n">
         <v>-0.0208</v>
@@ -1000,10 +1000,10 @@
         <v>2.3284</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0195</v>
+        <v>0.4795</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2146</v>
+        <v>0.6746</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1951</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1787</v>
+        <v>1.0024</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3817</v>
+        <v>2.0419</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2031</v>
+        <v>-1.0395</v>
       </c>
       <c r="G8" t="n">
         <v>0.7171</v>
@@ -1078,13 +1078,13 @@
         <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.305</v>
+        <v>-0.0348</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2196</v>
+        <v>-0.0561</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1761</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MATÍAS RODRÍGUEZ</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.194</v>
+        <v>0.4555</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.0017</v>
       </c>
       <c r="F9" t="n">
-        <v>0.194</v>
+        <v>0.4573</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-1.9931</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.3576</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-2.3506</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-1.1179</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.8156</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.9335</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.8752</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.4581</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.4171</v>
       </c>
       <c r="P9" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.0606</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.1077</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1683</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.194</v>
+        <v>0.2941</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="F10" t="n">
         <v>0.194</v>
@@ -1234,10 +1234,10 @@
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>G. MATÍAS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6239</v>
+        <v>0.2941</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8631</v>
+        <v>0.1001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2392</v>
+        <v>0.194</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9931</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3576</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3506</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1179</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8156</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9335</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8752</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4581</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4171</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0188</v>
+        <v>0.1001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9691</v>
+        <v>0.1001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0498</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8939</v>
+        <v>-1.1519</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3896</v>
+        <v>-2.7295</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4958</v>
+        <v>1.5775</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3535</v>
@@ -1390,13 +1390,13 @@
         <v>1.3582</v>
       </c>
       <c r="S12" t="n">
-        <v>0.188</v>
+        <v>-0.0701</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4262</v>
+        <v>0.0863</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2382</v>
+        <v>-0.1564</v>
       </c>
       <c r="V12" t="n">
         <v>0.0478</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2038</v>
+        <v>-1.498</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5179</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6859</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8958</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3158</v>
+        <v>0.0216</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5473</v>
+        <v>0.3076</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2315</v>
+        <v>-0.286</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5642</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.7441</v>
+        <v>19.35</v>
       </c>
       <c r="E14" t="n">
-        <v>14.8729</v>
+        <v>15.4784</v>
       </c>
       <c r="F14" t="n">
-        <v>3.871599999999999</v>
+        <v>3.871499999999999</v>
       </c>
       <c r="G14" t="n">
         <v>8.989599999999999</v>
@@ -1528,7 +1528,7 @@
         <v>0.2226999999999997</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.604799999999999</v>
+        <v>-4.6048</v>
       </c>
       <c r="N14" t="n">
         <v>-1.7961</v>
@@ -1546,16 +1546,16 @@
         <v>16.4927</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3367</v>
+        <v>3.942499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1681</v>
+        <v>3.774</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1684</v>
+        <v>0.1685</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3732</v>
+        <v>-0.3731999999999998</v>
       </c>
       <c r="W14" t="n">
         <v>7.8119</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8261</v>
+        <v>2.8528</v>
       </c>
       <c r="E15" t="n">
-        <v>4.107</v>
+        <v>3.8067</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2809</v>
+        <v>-0.9539</v>
       </c>
       <c r="G15" t="n">
         <v>1.473</v>
@@ -1624,13 +1624,13 @@
         <v>0.5821</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2068</v>
+        <v>0.2336</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3656</v>
+        <v>0.0653</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1588</v>
+        <v>0.1683</v>
       </c>
       <c r="V15" t="n">
         <v>0.5642</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9895</v>
+        <v>1.4627</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5289</v>
+        <v>2.0294</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5394</v>
+        <v>-0.5666</v>
       </c>
       <c r="G16" t="n">
         <v>1.4951</v>
@@ -1702,13 +1702,13 @@
         <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4011</v>
+        <v>-0.9278</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1508</v>
+        <v>-0.6503</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2503</v>
+        <v>-0.2776</v>
       </c>
       <c r="V16" t="n">
         <v>2.4477</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2848</v>
+        <v>-1.2227</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7891</v>
+        <v>-1.0142</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0739</v>
+        <v>-0.2084</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9327</v>
+        <v>-0.2584</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2274</v>
+        <v>-0.7522</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1601</v>
+        <v>0.4938</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3567</v>
+        <v>0.6455</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5819</v>
+        <v>0.6632</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9386</v>
+        <v>-0.0178</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5759</v>
+        <v>-0.9038</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3545</v>
+        <v>-1.4154</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7785</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
         <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7703</v>
+        <v>-0.2762</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7907</v>
+        <v>-0.0014</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0204</v>
+        <v>-0.2748</v>
       </c>
       <c r="V17" t="n">
-        <v>1.788</v>
+        <v>0.2821</v>
       </c>
       <c r="W17" t="n">
-        <v>4.2358</v>
+        <v>0.2821</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5367</v>
+        <v>-1.9127</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3237</v>
+        <v>0.1885</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2129</v>
+        <v>-2.1012</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5192</v>
+        <v>-0.9327</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.3167</v>
+        <v>0.2274</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2024</v>
+        <v>-1.1601</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1711</v>
+        <v>-0.3567</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2523</v>
+        <v>1.5819</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08119999999999999</v>
+        <v>-1.9386</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3481</v>
+        <v>-0.5759</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0645</v>
+        <v>-1.3545</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2836</v>
+        <v>0.7785</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5821</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.8806</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0601</v>
+        <v>0.1424</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0011</v>
+        <v>0.1901</v>
       </c>
       <c r="U18" t="n">
-        <v>1.059</v>
+        <v>-0.0476</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6597</v>
+        <v>1.788</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8462</v>
+        <v>4.2358</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.506</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5775</v>
+        <v>-1.9975</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3145</v>
+        <v>-0.4097</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2629</v>
+        <v>-1.5878</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2584</v>
+        <v>-0.9757</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7522</v>
+        <v>-2.5128</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4938</v>
+        <v>1.5371</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6455</v>
+        <v>1.3293</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6632</v>
+        <v>-0.5026</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0178</v>
+        <v>1.8319</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9038</v>
+        <v>-2.305</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4154</v>
+        <v>-2.0103</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.2948</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9702</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.631</v>
+        <v>-0.4397</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3017</v>
+        <v>0.2013</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3293</v>
+        <v>-0.641</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4975</v>
+        <v>-2.0545</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6099</v>
+        <v>-0.3237</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8876</v>
+        <v>-1.7308</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9757</v>
+        <v>-2.5192</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5128</v>
+        <v>-2.3167</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5371</v>
+        <v>-0.2024</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3293</v>
+        <v>-1.1711</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5026</v>
+        <v>-1.2523</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8319</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.305</v>
+        <v>-1.3481</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0103</v>
+        <v>-1.0645</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2948</v>
+        <v>-0.2836</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5821</v>
+        <v>0.5821</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9397</v>
+        <v>0.5423</v>
       </c>
       <c r="T20" t="n">
         <v>0.0011</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9408</v>
+        <v>0.5412</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7718</v>
+        <v>-3.5443</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7903</v>
+        <v>-2.5901</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9815</v>
+        <v>-0.9542</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0213</v>
@@ -2092,13 +2092,13 @@
         <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1101</v>
+        <v>-0.8827</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3017</v>
+        <v>-0.1015</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8084</v>
+        <v>-0.7811</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9003</v>
+        <v>-5.4186</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4338</v>
+        <v>-2.7341</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4665</v>
+        <v>-2.6845</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8845</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5099</v>
+        <v>-1.0282</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4262</v>
+        <v>0.1259</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-1.1541</v>
       </c>
       <c r="V22" t="n">
         <v>-0.894</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9914</v>
+        <v>-6.9096</v>
       </c>
       <c r="E23" t="n">
         <v>-2.8242</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.1672</v>
+        <v>-4.0854</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3659</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7822</v>
+        <v>-0.7004</v>
       </c>
       <c r="T23" t="n">
         <v>0.0011</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7833</v>
+        <v>-0.7015</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8731</v>
@@ -2284,7 +2284,7 @@
         <v>-18.7444</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8714</v>
+        <v>-3.871400000000001</v>
       </c>
       <c r="F24" t="n">
         <v>-14.8728</v>
@@ -2317,7 +2317,7 @@
         <v>-0.2226999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.7912</v>
+        <v>-6.791200000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-16.4927</v>
@@ -2326,16 +2326,16 @@
         <v>9.701700000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.3368</v>
+        <v>-3.3367</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1684000000000002</v>
+        <v>-0.1684</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.1683</v>
+        <v>-3.168200000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3731</v>
+        <v>0.3731000000000009</v>
       </c>
       <c r="W24" t="n">
         <v>8.184899999999999</v>
